--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_AS MONACO.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_AS MONACO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA36"/>
+  <dimension ref="A1:BA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.1974921630094044</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
@@ -752,13 +752,13 @@
         <v>0.7226277372262774</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.023255813953488</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.724137931034483</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
         <v>1.39344262295082</v>
@@ -801,13 +801,13 @@
         <v>0.1974921630094044</v>
       </c>
       <c r="J3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="M3" t="n">
         <v>11.2</v>
@@ -882,13 +882,13 @@
         <v>0.7226277372262773</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.023255813953488</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.724137931034483</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
         <v>1.39344262295082</v>
@@ -931,13 +931,13 @@
         <v>0.142433234421365</v>
       </c>
       <c r="J4" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
@@ -1012,13 +1012,13 @@
         <v>1.117647058823529</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7213114754098361</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.192982456140351</v>
+        <v>0.08771929824561403</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.090909090909091</v>
+        <v>3</v>
       </c>
       <c r="AN4" t="n">
         <v>1.796296296296296</v>
@@ -1061,13 +1061,13 @@
         <v>0.142433234421365</v>
       </c>
       <c r="J5" t="n">
-        <v>8.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>13.6</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>9.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="M5" t="n">
         <v>9.800000000000001</v>
@@ -1142,13 +1142,13 @@
         <v>1.117647058823529</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7213114754098362</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.192982456140351</v>
+        <v>0.08771929824561403</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.09090909090909</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
         <v>1.796296296296296</v>
@@ -1486,16 +1486,16 @@
         <v>31</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>8</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>226:39</t>
+          <t>126:34</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.124</v>
+        <v>0.222</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.041</v>
+        <v>0.073</v>
       </c>
       <c r="BA8" t="n">
         <v>0.123</v>
@@ -1651,16 +1651,16 @@
         <v>59</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>16</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>290:29</t>
+          <t>148:47</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.019</v>
+        <v>0.037</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06</v>
+        <v>0.117</v>
       </c>
       <c r="BA9" t="n">
         <v>0.053</v>
@@ -1816,16 +1816,16 @@
         <v>30</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>132:44</t>
+          <t>61:01</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>8.667</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.109</v>
+        <v>0.236</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.033</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.191</v>
       </c>
       <c r="BA10" t="n">
         <v>0.008</v>
@@ -1981,16 +1981,16 @@
         <v>53</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>15</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>108:16</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.119</v>
+        <v>0.219</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.022</v>
+        <v>0.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.076</v>
+        <v>0.14</v>
       </c>
       <c r="BA11" t="n">
         <v>0.008</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>17</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>179:26</t>
+          <t>89:27</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.074</v>
+        <v>0.148</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.055</v>
+        <v>0.11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.065</v>
+        <v>0.13</v>
       </c>
       <c r="BA12" t="n">
         <v>0.008</v>
@@ -2311,10 +2311,10 @@
         <v>31</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>133:21</t>
+          <t>53:24</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.062</v>
+        <v>0.154</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.049</v>
+        <v>0.123</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.096</v>
+        <v>0.24</v>
       </c>
       <c r="BA13" t="n">
         <v>0.008</v>
@@ -2476,16 +2476,16 @@
         <v>9</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>8</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>179:43</t>
+          <t>79:40</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>10.333</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.083</v>
+        <v>0.187</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.024</v>
+        <v>0.055</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.065</v>
+        <v>0.146</v>
       </c>
       <c r="BA14" t="n">
         <v>0.038</v>
@@ -2647,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>81:56</t>
+          <t>40:57</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>7.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.083</v>
+        <v>0.166</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
       <c r="BA15" t="n">
         <v>0.022</v>
@@ -2806,16 +2806,16 @@
         <v>52</v>
       </c>
       <c r="U16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>18</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>276:03</t>
+          <t>135:18</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.101</v>
+        <v>0.206</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.042</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="BA16" t="n">
         <v>0.151</v>
@@ -2971,16 +2971,16 @@
         <v>112</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>23</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>308:19</t>
+          <t>156:36</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>4.211</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.118</v>
+        <v>0.233</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.079</v>
+        <v>0.156</v>
       </c>
       <c r="BA17" t="n">
         <v>0.292</v>
@@ -3240,163 +3240,163 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="T19" t="n">
+        <v>422</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>121</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>153</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE19" t="n">
         <v>9</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>2</v>
+        <v>412.56</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>0.487</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>0.907</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.393</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>6.623</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="BA19" t="n">
         <v>0</v>
@@ -3405,44 +3405,44 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="D20" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E20" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J20" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K20" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="M20" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="N20" t="n">
         <v>19</v>
@@ -3451,76 +3451,76 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="Q20" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="R20" t="n">
         <v>79</v>
       </c>
       <c r="S20" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T20" t="n">
-        <v>422</v>
+        <v>565</v>
       </c>
       <c r="U20" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Z20" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.791</v>
+        <v>0.879</v>
       </c>
       <c r="AB20" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AC20" t="n">
         <v>75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.52</v>
+        <v>0.467</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
         <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.529</v>
+        <v>0.235</v>
       </c>
       <c r="AH20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AI20" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.308</v>
+        <v>0.333</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="AL20" t="n">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.225</v>
+        <v>0.377</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -3528,40 +3528,40 @@
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>412.56</v>
+        <v>420.48</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.487</v>
+        <v>0.592</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.532</v>
+        <v>0.61</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.907</v>
+        <v>1.063</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.148</v>
+        <v>0.128</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.197</v>
+        <v>0.142</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.393</v>
+        <v>1.796</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.23</v>
+        <v>6.241</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.623</v>
+        <v>8.037000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>0.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.047</v>
+        <v>0.066</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.134</v>
+        <v>0.153</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -3570,655 +3570,655 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>447</v>
-      </c>
-      <c r="D21" t="n">
-        <v>114</v>
-      </c>
-      <c r="E21" t="n">
-        <v>184</v>
-      </c>
-      <c r="F21" t="n">
-        <v>57</v>
-      </c>
-      <c r="G21" t="n">
-        <v>153</v>
-      </c>
-      <c r="H21" t="n">
-        <v>48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>67</v>
-      </c>
-      <c r="J21" t="n">
-        <v>97</v>
-      </c>
-      <c r="K21" t="n">
-        <v>140</v>
-      </c>
-      <c r="L21" t="n">
-        <v>57</v>
-      </c>
-      <c r="M21" t="n">
-        <v>37</v>
-      </c>
-      <c r="N21" t="n">
-        <v>19</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>49</v>
-      </c>
-      <c r="R21" t="n">
-        <v>79</v>
-      </c>
-      <c r="S21" t="n">
-        <v>86</v>
-      </c>
-      <c r="T21" t="n">
-        <v>565</v>
-      </c>
-      <c r="U21" t="n">
-        <v>44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>68</v>
-      </c>
-      <c r="W21" t="n">
-        <v>46</v>
-      </c>
-      <c r="X21" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>123</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>35</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>52</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>138</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>1000:00</t>
-        </is>
-      </c>
-      <c r="AO21" t="n">
-        <v>420.48</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0.592</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.796</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6.241</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>8.037000000000001</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
+          <t>#0 E. OKOBO (Per Game)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>31</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>25:18</t>
+        </is>
+      </c>
+      <c r="AO22" t="n">
+        <v>11.616</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.123</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>#0 E. OKOBO (Per Game)</t>
+          <t>#4 J. BLOSSOMGAME (Per Game)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>8.6</v>
+        <v>11.6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.8</v>
       </c>
-      <c r="G23" t="n">
+      <c r="J23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>59</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.4</v>
       </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AC23" t="n">
         <v>2.4</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>31</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AD23" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI23" t="n">
         <v>0.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AJ23" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
       </c>
       <c r="AK23" t="n">
         <v>0.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>45:19</t>
+          <t>29:45</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>11.616</v>
+        <v>10.352</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.422</v>
+        <v>0.598</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.447</v>
+        <v>0.607</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.74</v>
+        <v>1.121</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.172</v>
+        <v>0.077</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.111</v>
+        <v>0.065</v>
       </c>
       <c r="AU23" t="n">
         <v>1.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.124</v>
+        <v>0.169</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.041</v>
+        <v>0.117</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.123</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#4 J. BLOSSOMGAME (Per Game)</t>
+          <t>#10 D. THEIS (Per Game)</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E24" t="n">
         <v>5</v>
       </c>
-      <c r="C24" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5.4</v>
-      </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2</v>
+        <v>0.25</v>
       </c>
       <c r="K24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>30</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3</v>
       </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>59</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AA24" t="n">
-        <v>0.889</v>
+        <v>0.833</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.583</v>
+        <v>0.556</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AU24" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>58:05</t>
-        </is>
-      </c>
-      <c r="AO24" t="n">
-        <v>10.352</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.121</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>8.333</v>
       </c>
       <c r="AW24" t="n">
-        <v>13</v>
+        <v>8.667</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.236</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.019</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.06</v>
+        <v>0.191</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.053</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#10 D. THEIS (Per Game)</t>
+          <t>#11 A. DIALLO (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>7.25</v>
+        <v>11.5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.25</v>
+        <v>5.25</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="J25" t="n">
         <v>0.25</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="R25" t="n">
         <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.833</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.556</v>
+        <v>0.75</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -4227,787 +4227,787 @@
         <v>0.25</v>
       </c>
       <c r="AI25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>27:04</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AU25" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>33:11</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AV25" t="n">
-        <v>8.333</v>
+        <v>21.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.667</v>
+        <v>22</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.109</v>
+        <v>0.219</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.033</v>
+        <v>0.04</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#11 A. DIALLO (Per Game)</t>
+          <t>#13 K. HAYES (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="D26" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="E26" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I26" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="J26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="K26" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="R26" t="n">
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="T26" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AU26" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>50:00</t>
-        </is>
-      </c>
-      <c r="AO26" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV26" t="n">
-        <v>21.5</v>
+        <v>4.75</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.119</v>
+        <v>0.148</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.022</v>
+        <v>0.11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.076</v>
+        <v>0.13</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#13 K. HAYES (Per Game)</t>
+          <t>#22 T. TARPEY (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>6.4</v>
+        <v>4.75</v>
       </c>
       <c r="D27" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
       <c r="T27" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.773</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>35:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>5.48</v>
+        <v>4.25</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.632</v>
+        <v>0.633</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.168</v>
+        <v>1.118</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.146</v>
+        <v>0.118</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.074</v>
+        <v>0.154</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.055</v>
+        <v>0.123</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.065</v>
+        <v>0.24</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#22 T. TARPEY (Per Game)</t>
+          <t>#23 J. BEGARIN (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="D28" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="G28" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>0.25</v>
       </c>
-      <c r="K28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AO28" t="n">
+        <v>6.152</v>
+      </c>
+      <c r="AP28" t="n">
         <v>0.25</v>
       </c>
-      <c r="R28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>31</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>33:20</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.633</v>
-      </c>
       <c r="AQ28" t="n">
-        <v>0.633</v>
+        <v>0.288</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.118</v>
+        <v>0.52</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.118</v>
+        <v>0.098</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.5</v>
+        <v>1.667</v>
       </c>
       <c r="AV28" t="n">
-        <v>7.5</v>
+        <v>8.667</v>
       </c>
       <c r="AW28" t="n">
-        <v>8</v>
+        <v>10.333</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.062</v>
+        <v>0.187</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.049</v>
+        <v>0.055</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.096</v>
+        <v>0.146</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.01</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#23 J. BEGARIN (Per Game)</t>
+          <t>#26 N. NEDOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3.2</v>
-      </c>
       <c r="H29" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>9</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AM29" t="n">
         <v>0</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>35:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>6.152</v>
+        <v>3.5</v>
       </c>
       <c r="AP29" t="n">
         <v>0.25</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.288</v>
+        <v>0.25</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.52</v>
+        <v>0.429</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.098</v>
+        <v>0.143</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.667</v>
+        <v>6</v>
       </c>
       <c r="AW29" t="n">
-        <v>10.333</v>
+        <v>7.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.083</v>
+        <v>0.166</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.065</v>
+        <v>0.028</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.038</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#26 N. NEDOVIC (Per Game)</t>
+          <t>#32 M. STRAZEL (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S30" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
       <c r="T30" t="n">
-        <v>-8</v>
+        <v>52</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -5016,493 +5016,493 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.25</v>
+        <v>3.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="AD30" t="n">
         <v>0.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>27:03</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>3.5</v>
+        <v>11.52</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.25</v>
+        <v>0.378</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.25</v>
+        <v>0.473</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.429</v>
+        <v>0.781</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.143</v>
+        <v>0.174</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AV30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW30" t="n">
         <v>6</v>
       </c>
-      <c r="AW30" t="n">
-        <v>7.5</v>
-      </c>
       <c r="AX30" t="n">
-        <v>0.083</v>
+        <v>0.206</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.014</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.028</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#32 M. STRAZEL (Per Game)</t>
+          <t>#55 M. JAMES (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D31" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="E31" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>112</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.8</v>
       </c>
-      <c r="I31" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>52</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AD31" t="n">
-        <v>0.5</v>
+        <v>0.643</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF31" t="n">
         <v>0.6</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="AH31" t="n">
         <v>0.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
         <v>3.6</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.222</v>
+        <v>0.5</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>55:12</t>
+          <t>31:19</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>11.52</v>
+        <v>15.048</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.378</v>
+        <v>0.66</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.473</v>
+        <v>0.711</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.781</v>
+        <v>1.063</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.174</v>
+        <v>0.253</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.341</v>
+        <v>0.383</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.9</v>
+        <v>1.737</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.1</v>
+        <v>2.474</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>4.211</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.101</v>
+        <v>0.233</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.042</v>
+        <v>0.156</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.151</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#55 M. JAMES (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.821</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>61:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>15.048</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.063</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.253</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.383</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.737</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.474</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.211</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>74.8</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>1.2</v>
+        <v>23</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>8.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4</v>
+        <v>12.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5511,96 +5511,96 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>0.791</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>82.512</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>0.487</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>0.907</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.393</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>6.623</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="BA33" t="n">
         <v>0</v>
@@ -5609,495 +5609,165 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="T34" t="n">
-        <v>9</v>
+        <v>565</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>0.879</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>0.4</v>
+        <v>84.096</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.592</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.063</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.796</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>6.241</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>8.037000000000001</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="D35" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G35" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H35" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I35" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="J35" t="n">
-        <v>17</v>
-      </c>
-      <c r="K35" t="n">
-        <v>23</v>
-      </c>
-      <c r="L35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S35" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>422</v>
-      </c>
-      <c r="U35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W35" t="n">
-        <v>10</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>82.512</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.393</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>6.623</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="D36" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E36" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="F36" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G36" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="I36" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="K36" t="n">
-        <v>28</v>
-      </c>
-      <c r="L36" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="R36" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S36" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>565</v>
-      </c>
-      <c r="U36" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V36" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO36" t="n">
-        <v>84.096</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0.592</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1.796</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>6.241</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>8.037000000000001</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="BA36" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_AS MONACO.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_AS MONACO.xlsx
@@ -671,13 +671,13 @@
         <v>0.1974921630094044</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
@@ -752,13 +752,13 @@
         <v>0.7226277372262774</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.023255813953488</v>
       </c>
       <c r="AM2" t="n">
-        <v>3</v>
+        <v>1.724137931034483</v>
       </c>
       <c r="AN2" t="n">
         <v>1.39344262295082</v>
@@ -801,13 +801,13 @@
         <v>0.1974921630094044</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>11.2</v>
@@ -882,13 +882,13 @@
         <v>0.7226277372262773</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.8148148148148149</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.023255813953488</v>
       </c>
       <c r="AM3" t="n">
-        <v>3</v>
+        <v>1.724137931034483</v>
       </c>
       <c r="AN3" t="n">
         <v>1.39344262295082</v>
@@ -931,13 +931,13 @@
         <v>0.142433234421365</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
@@ -1012,13 +1012,13 @@
         <v>1.117647058823529</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.7213114754098361</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.08771929824561403</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="AM4" t="n">
-        <v>3</v>
+        <v>2.043478260869565</v>
       </c>
       <c r="AN4" t="n">
         <v>1.796296296296296</v>
@@ -1061,13 +1061,13 @@
         <v>0.142433234421365</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>13.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="M5" t="n">
         <v>9.800000000000001</v>
@@ -1142,13 +1142,13 @@
         <v>1.117647058823529</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.7213114754098362</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.08771929824561403</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="AM5" t="n">
-        <v>3</v>
+        <v>2.043478260869565</v>
       </c>
       <c r="AN5" t="n">
         <v>1.796296296296296</v>
@@ -1486,16 +1486,16 @@
         <v>31</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="n">
         <v>8</v>
@@ -1651,16 +1651,16 @@
         <v>59</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="n">
         <v>16</v>
@@ -1816,16 +1816,16 @@
         <v>30</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
         <v>10</v>
@@ -1981,16 +1981,16 @@
         <v>53</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
         <v>15</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="n">
         <v>17</v>
@@ -2311,10 +2311,10 @@
         <v>31</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2476,16 +2476,16 @@
         <v>9</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>8</v>
@@ -2647,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
@@ -2806,16 +2806,16 @@
         <v>52</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
         <v>18</v>
@@ -2971,16 +2971,16 @@
         <v>112</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="n">
         <v>23</v>
@@ -3301,16 +3301,16 @@
         <v>422</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
         <v>121</v>
@@ -3466,16 +3466,16 @@
         <v>565</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="W20" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="n">
         <v>123</v>
@@ -3690,16 +3690,16 @@
         <v>31</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y22" t="n">
         <v>1.6</v>
@@ -3855,16 +3855,16 @@
         <v>59</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y23" t="n">
         <v>3.2</v>
@@ -4020,16 +4020,16 @@
         <v>30</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="Y24" t="n">
         <v>2.5</v>
@@ -4185,16 +4185,16 @@
         <v>53</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y25" t="n">
         <v>3.75</v>
@@ -4353,13 +4353,13 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y26" t="n">
         <v>3.4</v>
@@ -4515,10 +4515,10 @@
         <v>31</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4680,16 +4680,16 @@
         <v>9</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y28" t="n">
         <v>1.6</v>
@@ -4851,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y29" t="n">
         <v>0.25</v>
@@ -5010,16 +5010,16 @@
         <v>52</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
         <v>3.6</v>
@@ -5175,16 +5175,16 @@
         <v>112</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y31" t="n">
         <v>4.6</v>
@@ -5505,16 +5505,16 @@
         <v>422</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="X33" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="Y33" t="n">
         <v>24.2</v>
@@ -5670,16 +5670,16 @@
         <v>565</v>
       </c>
       <c r="U34" t="n">
-        <v>0.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>13.8</v>
       </c>
       <c r="W34" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="Y34" t="n">
         <v>24.6</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_AS MONACO.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_AS MONACO.xlsx
@@ -683,13 +683,13 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="O2" t="n">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4796238244514107</v>
+        <v>0.2821316614420062</v>
       </c>
       <c r="Q2" t="n">
         <v>39</v>
@@ -710,25 +710,25 @@
         <v>0.05329153605015674</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08150470219435736</v>
+        <v>0.09717868338557993</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.347962382445141</v>
+        <v>0.3322884012539185</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7908496732026143</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="AD2" t="n">
         <v>0.52</v>
@@ -737,13 +737,13 @@
         <v>0.5294117647058824</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2252252252252252</v>
+        <v>0.2264150943396226</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.581699346405229</v>
+        <v>1.288888888888889</v>
       </c>
       <c r="AI2" t="n">
         <v>1.058823529411765</v>
@@ -813,13 +813,13 @@
         <v>11.2</v>
       </c>
       <c r="N3" t="n">
-        <v>24.2</v>
+        <v>11.6</v>
       </c>
       <c r="O3" t="n">
-        <v>30.6</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4796238244514107</v>
+        <v>0.2821316614420063</v>
       </c>
       <c r="Q3" t="n">
         <v>7.8</v>
@@ -840,25 +840,25 @@
         <v>0.05329153605015674</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="X3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08150470219435738</v>
+        <v>0.09717868338557994</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.347962382445141</v>
+        <v>0.3322884012539185</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7908496732026143</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="AD3" t="n">
         <v>0.52</v>
@@ -867,13 +867,13 @@
         <v>0.5294117647058824</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2252252252252252</v>
+        <v>0.2264150943396226</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.581699346405229</v>
+        <v>1.288888888888889</v>
       </c>
       <c r="AI3" t="n">
         <v>1.058823529411765</v>
@@ -943,13 +943,13 @@
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4154302670623146</v>
+        <v>0.2729970326409495</v>
       </c>
       <c r="Q4" t="n">
         <v>35</v>
@@ -970,25 +970,25 @@
         <v>0.05044510385756677</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04451038575667656</v>
+        <v>0.04747774480712166</v>
       </c>
       <c r="Z4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA4" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4094955489614243</v>
+        <v>0.4065281899109792</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8785714285714286</v>
+        <v>0.8152173913043478</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4666666666666667</v>
@@ -997,13 +997,13 @@
         <v>0.2352941176470588</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3768115942028986</v>
+        <v>0.3722627737226277</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.757142857142857</v>
+        <v>1.630434782608696</v>
       </c>
       <c r="AI4" t="n">
         <v>0.4705882352941176</v>
@@ -1073,13 +1073,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>24.6</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>28</v>
+        <v>18.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4154302670623145</v>
+        <v>0.2729970326409495</v>
       </c>
       <c r="Q5" t="n">
         <v>7</v>
@@ -1100,25 +1100,25 @@
         <v>0.05044510385756676</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04451038575667655</v>
+        <v>0.04747774480712166</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4094955489614243</v>
+        <v>0.4065281899109792</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8785714285714287</v>
+        <v>0.8152173913043479</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4666666666666667</v>
@@ -1127,13 +1127,13 @@
         <v>0.2352941176470588</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3768115942028986</v>
+        <v>0.3722627737226277</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.757142857142857</v>
+        <v>1.630434782608696</v>
       </c>
       <c r="AI5" t="n">
         <v>0.4705882352941177</v>
@@ -1498,13 +1498,13 @@
         <v>7</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.667</v>
+        <v>0.429</v>
       </c>
       <c r="AB8" t="n">
         <v>6</v>
@@ -1525,22 +1525,22 @@
         <v>0.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.286</v>
+        <v>0.231</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>2</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.889</v>
+        <v>0.867</v>
       </c>
       <c r="AB9" t="n">
         <v>7</v>
@@ -1693,19 +1693,19 @@
         <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AK9" t="n">
         <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.25</v>
+        <v>0.308</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.833</v>
+        <v>0.75</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1993,13 +1993,13 @@
         <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AB11" t="n">
         <v>6</v>
@@ -2158,13 +2158,13 @@
         <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.773</v>
+        <v>0.643</v>
       </c>
       <c r="AB12" t="n">
         <v>2</v>
@@ -2488,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z14" t="n">
         <v>8</v>
       </c>
-      <c r="Z14" t="n">
-        <v>11</v>
-      </c>
       <c r="AA14" t="n">
-        <v>0.727</v>
+        <v>0.625</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2518,16 +2518,16 @@
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AB16" t="n">
         <v>3</v>
@@ -2983,13 +2983,13 @@
         <v>7</v>
       </c>
       <c r="Y17" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.821</v>
+        <v>0.5</v>
       </c>
       <c r="AB17" t="n">
         <v>9</v>
@@ -3313,13 +3313,13 @@
         <v>29</v>
       </c>
       <c r="Y19" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="Z19" t="n">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.791</v>
+        <v>0.644</v>
       </c>
       <c r="AB19" t="n">
         <v>39</v>
@@ -3340,22 +3340,22 @@
         <v>0.529</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.308</v>
+        <v>0.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>23</v>
       </c>
       <c r="Y20" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="Z20" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.879</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB20" t="n">
         <v>35</v>
@@ -3505,22 +3505,22 @@
         <v>0.235</v>
       </c>
       <c r="AH20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AK20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AL20" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.377</v>
+        <v>0.372</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -3702,13 +3702,13 @@
         <v>1.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.667</v>
+        <v>0.429</v>
       </c>
       <c r="AB22" t="n">
         <v>1.2</v>
@@ -3729,22 +3729,22 @@
         <v>0.8</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.286</v>
+        <v>0.231</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3867,13 +3867,13 @@
         <v>0.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.889</v>
+        <v>0.867</v>
       </c>
       <c r="AB23" t="n">
         <v>1.4</v>
@@ -3897,19 +3897,19 @@
         <v>0.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AK23" t="n">
         <v>0.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.25</v>
+        <v>0.308</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4032,13 +4032,13 @@
         <v>0.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.833</v>
+        <v>0.75</v>
       </c>
       <c r="AB24" t="n">
         <v>1.25</v>
@@ -4197,13 +4197,13 @@
         <v>0.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AB25" t="n">
         <v>1.5</v>
@@ -4362,13 +4362,13 @@
         <v>0.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.773</v>
+        <v>0.643</v>
       </c>
       <c r="AB26" t="n">
         <v>0.4</v>
@@ -4692,13 +4692,13 @@
         <v>0.2</v>
       </c>
       <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA28" t="n">
-        <v>0.727</v>
+        <v>0.625</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4722,16 +4722,16 @@
         <v>0.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AM28" t="n">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AB30" t="n">
         <v>0.6</v>
@@ -5187,13 +5187,13 @@
         <v>1.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.821</v>
+        <v>0.5</v>
       </c>
       <c r="AB31" t="n">
         <v>1.8</v>
@@ -5517,13 +5517,13 @@
         <v>5.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>24.2</v>
+        <v>11.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>30.6</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.791</v>
+        <v>0.644</v>
       </c>
       <c r="AB33" t="n">
         <v>7.8</v>
@@ -5544,22 +5544,22 @@
         <v>0.529</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.308</v>
+        <v>0.29</v>
       </c>
       <c r="AK33" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AL33" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>4.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>24.6</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>28</v>
+        <v>18.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.879</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB34" t="n">
         <v>7</v>
@@ -5709,22 +5709,22 @@
         <v>0.235</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AK34" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="AL34" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.377</v>
+        <v>0.372</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
